--- a/data_pipeline/trend_selection.xlsx
+++ b/data_pipeline/trend_selection.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\internship\airflow\dbt_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\internship\airflow\dbt_project\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A5FF87-DB08-41B9-B26E-ABE43233ABDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6444B657-C2E6-4B2F-AC9F-FA900AC41CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C76D77E7-994D-4C91-9B64-56FDF2609EB6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
   <si>
     <t>segmentation_version</t>
   </si>
@@ -93,6 +93,10 @@
   </si>
   <si>
     <t>2024-12-31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Why this trend?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -602,7 +606,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>17</v>
@@ -631,7 +635,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
@@ -640,7 +644,7 @@
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">

--- a/data_pipeline/trend_selection.xlsx
+++ b/data_pipeline/trend_selection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\internship\airflow\dbt_project\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6444B657-C2E6-4B2F-AC9F-FA900AC41CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDBD72F-B67F-4A6C-906A-053F3FD3A162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C76D77E7-994D-4C91-9B64-56FDF2609EB6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="20">
   <si>
     <t>segmentation_version</t>
   </si>
@@ -96,7 +96,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Why this trend?</t>
+    <t>Why this trend??</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -467,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC1E40D-C3D8-496F-B6D1-F759CCC8728E}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="8" width="10.69921875" bestFit="1" customWidth="1"/>
@@ -562,22 +562,22 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>17</v>
@@ -594,7 +594,7 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -606,7 +606,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>17</v>
@@ -615,37 +615,12 @@
         <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G7" s="1"/>
@@ -654,10 +629,6 @@
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
